--- a/NBFC-MF/FinancingInvesting.xlsx
+++ b/NBFC-MF/FinancingInvesting.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="59">
   <si>
     <t>Date</t>
   </si>
@@ -199,6 +199,9 @@
   </si>
   <si>
     <t>Deposit - Ranjit to be adjusted</t>
+  </si>
+  <si>
+    <t>Bor-Bechau-29jun26-01</t>
   </si>
 </sst>
 </file>
@@ -314,7 +317,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -357,6 +360,42 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -639,341 +678,368 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="31.42578125" style="2" customWidth="1"/>
-    <col min="5" max="6" width="19.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="2"/>
-    <col min="8" max="8" width="19.42578125" style="2" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="16.140625" style="25" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" style="25" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" style="25" customWidth="1"/>
+    <col min="4" max="4" width="31.42578125" style="25" customWidth="1"/>
+    <col min="5" max="6" width="19.140625" style="25" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="25"/>
+    <col min="8" max="8" width="19.42578125" style="25" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="25"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="9" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:6" s="23" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="17" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="15">
+      <c r="A2" s="18">
         <v>45180</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="19">
         <v>17500</v>
       </c>
-      <c r="F2" s="4"/>
+      <c r="F2" s="19"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="14">
+      <c r="A3" s="20">
         <v>45180</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="21">
         <v>17380</v>
       </c>
-      <c r="F3" s="6"/>
+      <c r="F3" s="21"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="15">
+      <c r="A4" s="18">
         <v>45256</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="19">
         <v>10000</v>
       </c>
-      <c r="F4" s="4"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="14">
+      <c r="A5" s="20">
         <v>45272</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="21">
         <v>35000</v>
       </c>
-      <c r="F5" s="6"/>
+      <c r="F5" s="21"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="15">
+      <c r="A6" s="18">
         <v>45274</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="19">
         <v>15000</v>
       </c>
-      <c r="F6" s="4"/>
+      <c r="F6" s="19"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="14">
+      <c r="A7" s="20">
         <v>45275</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="21">
         <v>40000</v>
       </c>
-      <c r="F7" s="6"/>
+      <c r="F7" s="21"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="15">
+      <c r="A8" s="18">
         <v>45278</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="19">
         <v>15000</v>
       </c>
-      <c r="F8" s="4"/>
+      <c r="F8" s="19"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="14">
+      <c r="A9" s="20">
         <v>45283</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="21">
         <v>10000</v>
       </c>
-      <c r="F9" s="6"/>
+      <c r="F9" s="21"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="15">
+      <c r="A10" s="18">
         <v>45322</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="19">
         <v>1500</v>
       </c>
-      <c r="F10" s="4"/>
+      <c r="F10" s="19"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="14">
+      <c r="A11" s="20">
         <v>45336</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="21">
         <v>12000</v>
       </c>
-      <c r="F11" s="6"/>
+      <c r="F11" s="21"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="15">
+      <c r="A12" s="18">
         <v>45368</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="19">
         <v>5000</v>
       </c>
-      <c r="F12" s="4"/>
+      <c r="F12" s="19"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="14">
+      <c r="A13" s="20">
         <v>45466</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="21" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="21" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="21">
         <v>10000</v>
       </c>
-      <c r="F13" s="6"/>
+      <c r="F13" s="21"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="15">
+      <c r="A14" s="18">
         <v>45647</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4" t="s">
+      <c r="B14" s="19"/>
+      <c r="C14" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="4">
+      <c r="E14" s="19">
         <v>10200</v>
       </c>
-      <c r="F14" s="4"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="14">
+      <c r="A15" s="20">
         <v>45647</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="21">
         <v>10000</v>
       </c>
-      <c r="F15" s="6"/>
+      <c r="F15" s="21"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="15">
+      <c r="A16" s="18">
         <v>46123</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="19">
         <v>80000</v>
       </c>
-      <c r="F16" s="4"/>
+      <c r="F16" s="19"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="14"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
+      <c r="A17" s="20">
+        <v>46202</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="21">
+        <v>160000</v>
+      </c>
+      <c r="F17" s="21"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="15"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="14"/>
+      <c r="B19" s="27"/>
+      <c r="C19" s="26"/>
+      <c r="D19" s="26"/>
+      <c r="E19" s="26"/>
+      <c r="F19" s="26"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="15"/>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="16"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6">
-        <f>SUM(E2:E18)</f>
-        <v>288580</v>
-      </c>
-      <c r="F19" s="6">
-        <f>SUM(F2:F18)</f>
+      <c r="E21" s="26">
+        <f>SUM(E2:E20)</f>
+        <v>448580</v>
+      </c>
+      <c r="F21" s="26">
+        <f>SUM(F2:F20)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <sheetProtection algorithmName="SHA-512" hashValue="pN5GUbJyUWgoOpdMQtkWLmj/woBob8nUPA3xTXRp/U5gNueaHDt1VhREosNcFzp3mG2N/mQB5FmdNm5yqb3BDA==" saltValue="N59xDSduS9dIldww4o7/9w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C16">
       <formula1>Financing</formula1>
     </dataValidation>
@@ -1224,7 +1290,7 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C18:C22 C2:C8 C9:C16">
       <formula1>Investing</formula1>
     </dataValidation>

--- a/NBFC-MF/FinancingInvesting.xlsx
+++ b/NBFC-MF/FinancingInvesting.xlsx
@@ -8,8 +8,9 @@
   </bookViews>
   <sheets>
     <sheet name="FinancingJournal" sheetId="1" r:id="rId1"/>
-    <sheet name="InvestingJournal" sheetId="3" r:id="rId2"/>
-    <sheet name="list" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
+    <sheet name="InvestingJournal" sheetId="3" r:id="rId3"/>
+    <sheet name="list" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="Financing">list!$B$6:$B$8</definedName>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="70">
   <si>
     <t>Date</t>
   </si>
@@ -202,6 +203,39 @@
   </si>
   <si>
     <t>Bor-Bechau-29jun26-01</t>
+  </si>
+  <si>
+    <t>Bor-Bechau-18jul26-01</t>
+  </si>
+  <si>
+    <t>Bor-Chaoba-18jul-01</t>
+  </si>
+  <si>
+    <t>Deposit-Chaoba</t>
+  </si>
+  <si>
+    <t>Bor-chaoba-21jun26-01</t>
+  </si>
+  <si>
+    <t>Wit-chaoba-22jul26-01</t>
+  </si>
+  <si>
+    <t>Withdrawal</t>
+  </si>
+  <si>
+    <t>Withdrawal-Chaoba</t>
+  </si>
+  <si>
+    <t>Izr-Anand-22jun26-01</t>
+  </si>
+  <si>
+    <t>Deposit-Aboong</t>
+  </si>
+  <si>
+    <t>Bor-Aboong-22jul-01</t>
+  </si>
+  <si>
+    <t>Bor-Aboong-21jun26-01</t>
   </si>
 </sst>
 </file>
@@ -317,7 +351,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -396,6 +430,10 @@
     </xf>
     <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -678,6 +716,448 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" style="25" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" style="25" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" style="25" customWidth="1"/>
+    <col min="4" max="4" width="31.42578125" style="25" customWidth="1"/>
+    <col min="5" max="6" width="19.140625" style="25" customWidth="1"/>
+    <col min="7" max="7" width="14" style="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.42578125" style="25" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="25"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="23" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="17" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="17" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="18">
+        <v>45180</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="19">
+        <v>17500</v>
+      </c>
+      <c r="F2" s="19"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="20">
+        <v>45180</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="21">
+        <v>17380</v>
+      </c>
+      <c r="F3" s="21"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="18">
+        <v>45256</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="19">
+        <v>10000</v>
+      </c>
+      <c r="F4" s="19"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="20">
+        <v>45272</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="21">
+        <v>35000</v>
+      </c>
+      <c r="F5" s="21"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="18">
+        <v>45274</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="19">
+        <v>15000</v>
+      </c>
+      <c r="F6" s="19"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="20">
+        <v>45275</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="21">
+        <v>40000</v>
+      </c>
+      <c r="F7" s="21"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="18">
+        <v>45278</v>
+      </c>
+      <c r="B8" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="19">
+        <v>15000</v>
+      </c>
+      <c r="F8" s="19"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="20">
+        <v>45283</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="21">
+        <v>10000</v>
+      </c>
+      <c r="F9" s="21"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="18">
+        <v>45322</v>
+      </c>
+      <c r="B10" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="19">
+        <v>1500</v>
+      </c>
+      <c r="F10" s="19"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="20">
+        <v>45336</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="21">
+        <v>12000</v>
+      </c>
+      <c r="F11" s="21"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="18">
+        <v>45368</v>
+      </c>
+      <c r="B12" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="E12" s="19">
+        <v>5000</v>
+      </c>
+      <c r="F12" s="19"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="20">
+        <v>45466</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="21">
+        <v>10000</v>
+      </c>
+      <c r="F13" s="21"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="18">
+        <v>45647</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="19">
+        <v>10200</v>
+      </c>
+      <c r="F14" s="19"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="20">
+        <v>45647</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="21">
+        <v>10000</v>
+      </c>
+      <c r="F15" s="21"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="18">
+        <v>46123</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="19">
+        <v>80000</v>
+      </c>
+      <c r="F16" s="19"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="18">
+        <v>46194</v>
+      </c>
+      <c r="B17" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="19">
+        <v>30000</v>
+      </c>
+      <c r="F17" s="19"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="18">
+        <v>46194</v>
+      </c>
+      <c r="B18" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="19">
+        <v>8000</v>
+      </c>
+      <c r="F18" s="19"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="20">
+        <v>46202</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="E19" s="21">
+        <v>160000</v>
+      </c>
+      <c r="F19" s="21"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="15">
+        <v>46222</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E20" s="24">
+        <v>92500</v>
+      </c>
+      <c r="F20" s="24"/>
+      <c r="G20" s="29">
+        <f>E16+E19+E20</f>
+        <v>332500</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="14">
+        <v>46225</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="26" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>65</v>
+      </c>
+      <c r="E21" s="26">
+        <v>-30000</v>
+      </c>
+      <c r="F21" s="26"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="15">
+        <v>46225</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="E22" s="24">
+        <v>89800</v>
+      </c>
+      <c r="F22" s="24"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="16"/>
+      <c r="B23" s="27"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="26">
+        <f>SUM(E2:E22)</f>
+        <v>638880</v>
+      </c>
+      <c r="F23" s="26">
+        <f>SUM(F2:F22)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C18">
+      <formula1>Financing</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -998,19 +1478,39 @@
       <c r="F17" s="21"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="15"/>
-      <c r="B18" s="24"/>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
+      <c r="A18" s="15">
+        <v>46221</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="E18" s="24">
+        <v>92500</v>
+      </c>
       <c r="F18" s="24"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="14"/>
-      <c r="B19" s="27"/>
-      <c r="C19" s="26"/>
-      <c r="D19" s="26"/>
-      <c r="E19" s="26"/>
+      <c r="A19" s="14">
+        <v>46221</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="E19" s="26">
+        <v>38000</v>
+      </c>
       <c r="F19" s="26"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -1030,7 +1530,7 @@
       </c>
       <c r="E21" s="26">
         <f>SUM(E2:E20)</f>
-        <v>448580</v>
+        <v>579080</v>
       </c>
       <c r="F21" s="26">
         <f>SUM(F2:F20)</f>
@@ -1038,20 +1538,18 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="pN5GUbJyUWgoOpdMQtkWLmj/woBob8nUPA3xTXRp/U5gNueaHDt1VhREosNcFzp3mG2N/mQB5FmdNm5yqb3BDA==" saltValue="N59xDSduS9dIldww4o7/9w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C16">
       <formula1>Financing</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.140625" style="2" customWidth="1"/>
@@ -1059,10 +1557,12 @@
     <col min="3" max="3" width="23.140625" style="2" customWidth="1"/>
     <col min="4" max="4" width="31.42578125" style="2" customWidth="1"/>
     <col min="5" max="6" width="19.140625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="9.140625" style="2"/>
+    <col min="8" max="8" width="14" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="9" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="9" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1082,7 +1582,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="15">
         <v>45473</v>
       </c>
@@ -1100,7 +1600,7 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="14">
         <v>46033</v>
       </c>
@@ -1119,7 +1619,7 @@
         <v>45350</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="15">
         <v>45853</v>
       </c>
@@ -1137,7 +1637,7 @@
         <v>300000</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="14">
         <v>45853</v>
       </c>
@@ -1155,7 +1655,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="15">
         <v>46066</v>
       </c>
@@ -1173,7 +1673,7 @@
         <v>190000</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="14">
         <v>46112</v>
       </c>
@@ -1191,7 +1691,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="15">
         <v>46157</v>
       </c>
@@ -1209,15 +1709,25 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="14"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A9" s="14">
+        <v>46225</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>39</v>
+      </c>
       <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F9" s="6">
+        <v>14650</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="15"/>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -1225,7 +1735,7 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="14"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -1233,15 +1743,16 @@
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="15"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="H12" s="28"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="14"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -1249,7 +1760,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="15"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -1257,7 +1768,7 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="14"/>
       <c r="B15" s="7"/>
       <c r="C15" s="6"/>
@@ -1265,7 +1776,7 @@
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="15"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -1286,12 +1797,12 @@
       </c>
       <c r="F17" s="6">
         <f>SUM(F2:F16)</f>
-        <v>735350</v>
+        <v>750000</v>
       </c>
     </row>
   </sheetData>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C18:C22 C2:C8 C9:C16">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C18:C22 C2:C16">
       <formula1>Investing</formula1>
     </dataValidation>
   </dataValidations>
@@ -1300,7 +1811,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C8"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>

--- a/NBFC-MF/FinancingInvesting.xlsx
+++ b/NBFC-MF/FinancingInvesting.xlsx
@@ -4,17 +4,17 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="FinancingJournal" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId2"/>
+    <sheet name="Depositors" sheetId="5" r:id="rId1"/>
+    <sheet name="FinancingJournal" sheetId="1" r:id="rId2"/>
     <sheet name="InvestingJournal" sheetId="3" r:id="rId3"/>
     <sheet name="list" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="Financing">list!$B$6:$B$8</definedName>
-    <definedName name="Investing">list!$B$2:$B$5</definedName>
+    <definedName name="Financing">list!$B$7:$B$9</definedName>
+    <definedName name="Investing">list!$B$2:$B$6</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="79">
   <si>
     <t>Date</t>
   </si>
@@ -199,18 +199,12 @@
     <t>Adv-Nao-15May26-01</t>
   </si>
   <si>
-    <t>Deposit - Ranjit to be adjusted</t>
-  </si>
-  <si>
     <t>Bor-Bechau-29jun26-01</t>
   </si>
   <si>
     <t>Bor-Bechau-18jul26-01</t>
   </si>
   <si>
-    <t>Bor-Chaoba-18jul-01</t>
-  </si>
-  <si>
     <t>Deposit-Chaoba</t>
   </si>
   <si>
@@ -236,6 +230,39 @@
   </si>
   <si>
     <t>Bor-Aboong-21jun26-01</t>
+  </si>
+  <si>
+    <t>Bor-Aboong-31jul-01</t>
+  </si>
+  <si>
+    <t>PunfamFoods-31jul-01</t>
+  </si>
+  <si>
+    <t>Investment to Unit</t>
+  </si>
+  <si>
+    <t>Investment to Punfam Units</t>
+  </si>
+  <si>
+    <t>Piglet Deposit to Suresh</t>
+  </si>
+  <si>
+    <t>Bor-Aboong-31jul-02</t>
+  </si>
+  <si>
+    <t>Aboong</t>
+  </si>
+  <si>
+    <t>Bechau</t>
+  </si>
+  <si>
+    <t>Benao</t>
+  </si>
+  <si>
+    <t>Chaoba</t>
+  </si>
+  <si>
+    <t>PunfamFoods-5aug-01</t>
   </si>
 </sst>
 </file>
@@ -351,12 +378,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -372,10 +398,6 @@
     <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -432,7 +454,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -716,436 +737,707 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.140625" style="25" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" style="25" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" style="25" customWidth="1"/>
-    <col min="4" max="4" width="31.42578125" style="25" customWidth="1"/>
-    <col min="5" max="6" width="19.140625" style="25" customWidth="1"/>
-    <col min="7" max="7" width="14" style="25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.42578125" style="25" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="25"/>
+    <col min="1" max="1" width="14.28515625" style="22" customWidth="1"/>
+    <col min="2" max="5" width="17.28515625" style="22" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="23" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:5" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="17">
+        <v>45620</v>
+      </c>
+      <c r="B2" s="18">
+        <v>10200</v>
+      </c>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="17">
+        <v>46194</v>
+      </c>
+      <c r="B3" s="18">
+        <v>8000</v>
+      </c>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="17">
+        <v>46225</v>
+      </c>
+      <c r="B4" s="18">
+        <v>89800</v>
+      </c>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="17">
+        <v>46202</v>
+      </c>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18">
+        <v>80000</v>
+      </c>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="17">
+        <v>46222</v>
+      </c>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18">
+        <v>160000</v>
+      </c>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="17">
+        <v>46234</v>
+      </c>
+      <c r="B7" s="18">
+        <v>20000</v>
+      </c>
+      <c r="C7" s="18">
+        <v>92500</v>
+      </c>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="17">
+        <v>46234</v>
+      </c>
+      <c r="B8" s="18">
+        <v>3000</v>
+      </c>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="18">
+        <f>SUM(B2:B16)</f>
+        <v>131000</v>
+      </c>
+      <c r="C17" s="18">
+        <f>SUM(C2:C16)</f>
+        <v>332500</v>
+      </c>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" style="22" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" style="22" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" style="22" customWidth="1"/>
+    <col min="4" max="4" width="31.42578125" style="22" customWidth="1"/>
+    <col min="5" max="6" width="19.140625" style="22" customWidth="1"/>
+    <col min="7" max="7" width="14" style="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.42578125" style="22" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="22"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="20" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="14" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="18">
+      <c r="A2" s="15">
         <v>45180</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="19">
+      <c r="E2" s="16">
         <v>17500</v>
       </c>
-      <c r="F2" s="19"/>
+      <c r="F2" s="16"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="20">
+      <c r="A3" s="17">
         <v>45180</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="21">
+      <c r="E3" s="18">
         <v>17380</v>
       </c>
-      <c r="F3" s="21"/>
+      <c r="F3" s="18"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="18">
+      <c r="A4" s="15">
         <v>45256</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="19">
+      <c r="E4" s="16">
         <v>10000</v>
       </c>
-      <c r="F4" s="19"/>
+      <c r="F4" s="16"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="20">
+      <c r="A5" s="17">
         <v>45272</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="21">
+      <c r="E5" s="18">
         <v>35000</v>
       </c>
-      <c r="F5" s="21"/>
+      <c r="F5" s="18"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="18">
+      <c r="A6" s="15">
         <v>45274</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="19">
+      <c r="E6" s="16">
         <v>15000</v>
       </c>
-      <c r="F6" s="19"/>
+      <c r="F6" s="16"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="20">
+      <c r="A7" s="17">
         <v>45275</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="21">
+      <c r="E7" s="18">
         <v>40000</v>
       </c>
-      <c r="F7" s="21"/>
+      <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="18">
+      <c r="A8" s="15">
         <v>45278</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="19">
+      <c r="E8" s="16">
         <v>15000</v>
       </c>
-      <c r="F8" s="19"/>
+      <c r="F8" s="16"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="20">
+      <c r="A9" s="17">
         <v>45283</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="18">
         <v>10000</v>
       </c>
-      <c r="F9" s="21"/>
+      <c r="F9" s="18"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="18">
+      <c r="A10" s="15">
         <v>45322</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="19">
+      <c r="E10" s="16">
         <v>1500</v>
       </c>
-      <c r="F10" s="19"/>
+      <c r="F10" s="16"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="20">
+      <c r="A11" s="17">
         <v>45336</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="18">
         <v>12000</v>
       </c>
-      <c r="F11" s="21"/>
+      <c r="F11" s="18"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="18">
+      <c r="A12" s="15">
         <v>45368</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E12" s="19">
+      <c r="E12" s="16">
         <v>5000</v>
       </c>
-      <c r="F12" s="19"/>
+      <c r="F12" s="16"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="20">
+      <c r="A13" s="17">
         <v>45466</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="21">
+      <c r="E13" s="18">
         <v>10000</v>
       </c>
-      <c r="F13" s="21"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="18">
+      <c r="A14" s="15">
         <v>45647</v>
       </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19" t="s">
+      <c r="B14" s="16"/>
+      <c r="C14" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D14" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="16">
+        <v>10200</v>
+      </c>
+      <c r="F14" s="16"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="17">
+        <v>45647</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="18">
+        <v>10000</v>
+      </c>
+      <c r="F15" s="18"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="15">
+        <v>46123</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="E16" s="16">
+        <v>80000</v>
+      </c>
+      <c r="F16" s="16"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="15">
+        <v>46194</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C17" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="16">
+        <v>30000</v>
+      </c>
+      <c r="F17" s="16"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="15">
+        <v>46194</v>
+      </c>
+      <c r="B18" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="E14" s="19">
-        <v>10200</v>
-      </c>
-      <c r="F14" s="19"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="20">
-        <v>45647</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="21" t="s">
+      <c r="C18" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="21">
-        <v>10000</v>
-      </c>
-      <c r="F15" s="21"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="18">
-        <v>46123</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="19" t="s">
+      <c r="D18" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="16">
+        <v>8000</v>
+      </c>
+      <c r="F18" s="16"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="17">
+        <v>46202</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D19" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="19">
-        <v>80000</v>
-      </c>
-      <c r="F16" s="19"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A17" s="18">
-        <v>46194</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C17" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="E17" s="19">
-        <v>30000</v>
-      </c>
-      <c r="F17" s="19"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A18" s="18">
-        <v>46194</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="19">
-        <v>8000</v>
-      </c>
-      <c r="F18" s="19"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A19" s="20">
-        <v>46202</v>
-      </c>
-      <c r="B19" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="E19" s="21">
+      <c r="E19" s="18">
         <v>160000</v>
       </c>
-      <c r="F19" s="21"/>
+      <c r="F19" s="18"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="15">
         <v>46222</v>
       </c>
-      <c r="B20" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="C20" s="24" t="s">
+      <c r="B20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="E20" s="24">
+      <c r="E20" s="16">
         <v>92500</v>
       </c>
-      <c r="F20" s="24"/>
-      <c r="G20" s="29">
-        <f>E16+E19+E20</f>
-        <v>332500</v>
-      </c>
+      <c r="F20" s="16"/>
+      <c r="G20" s="25"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A21" s="14">
+      <c r="A21" s="17">
         <v>46225</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="D21" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="C21" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" s="26" t="s">
-        <v>65</v>
-      </c>
-      <c r="E21" s="26">
+      <c r="E21" s="18">
         <v>-30000</v>
       </c>
-      <c r="F21" s="26"/>
+      <c r="F21" s="18"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="15">
         <v>46225</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E22" s="16">
+        <v>89800</v>
+      </c>
+      <c r="F22" s="16"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="12">
+        <v>46234</v>
+      </c>
+      <c r="B23" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C23" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D22" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="E22" s="24">
-        <v>89800</v>
-      </c>
-      <c r="F22" s="24"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="16"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="E23" s="21">
+        <v>20000</v>
+      </c>
+      <c r="F23" s="21"/>
+      <c r="G23" s="25"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="12">
+        <v>46234</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" s="21">
+        <v>3000</v>
+      </c>
+      <c r="F24" s="21"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="12"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="21"/>
+      <c r="D25" s="21"/>
+      <c r="E25" s="21"/>
+      <c r="F25" s="21"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="12"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="21"/>
+      <c r="D26" s="21"/>
+      <c r="E26" s="21"/>
+      <c r="F26" s="21"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="12"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="21"/>
+      <c r="D27" s="21"/>
+      <c r="E27" s="21"/>
+      <c r="F27" s="21"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" s="12"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="21"/>
+      <c r="D28" s="21"/>
+      <c r="E28" s="21"/>
+      <c r="F28" s="21"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" s="12"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" s="12"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" s="13"/>
+      <c r="B31" s="24"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E23" s="26">
-        <f>SUM(E2:E22)</f>
-        <v>638880</v>
-      </c>
-      <c r="F23" s="26">
+      <c r="E31" s="23">
+        <f>SUM(E2:E30)</f>
+        <v>661880</v>
+      </c>
+      <c r="F31" s="23">
         <f>SUM(F2:F22)</f>
         <v>0</v>
       </c>
     </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G32" s="25"/>
+    </row>
+    <row r="33" spans="7:7" x14ac:dyDescent="0.3">
+      <c r="G33" s="25"/>
+    </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="MJHUm5W/iuw+KYMBQeUmJSJlW+mJz07/RWmQxuj0cM+K7FMztoOwvgHi97SjfCIIRbe7ei/dcr5MUb+C/E0g0w==" saltValue="L2uZANE6DVQeaB2R+ucd8A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C18">
       <formula1>Financing</formula1>
@@ -1156,429 +1448,38 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F21"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="16.140625" style="25" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" style="25" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" style="25" customWidth="1"/>
-    <col min="4" max="4" width="31.42578125" style="25" customWidth="1"/>
-    <col min="5" max="6" width="19.140625" style="25" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="25"/>
-    <col min="8" max="8" width="19.42578125" style="25" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="25"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" s="23" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="18">
-        <v>45180</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="19">
-        <v>17500</v>
-      </c>
-      <c r="F2" s="19"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="20">
-        <v>45180</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="21">
-        <v>17380</v>
-      </c>
-      <c r="F3" s="21"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="18">
-        <v>45256</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="19">
-        <v>10000</v>
-      </c>
-      <c r="F4" s="19"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="20">
-        <v>45272</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="21">
-        <v>35000</v>
-      </c>
-      <c r="F5" s="21"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="18">
-        <v>45274</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="19">
-        <v>15000</v>
-      </c>
-      <c r="F6" s="19"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="20">
-        <v>45275</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="21">
-        <v>40000</v>
-      </c>
-      <c r="F7" s="21"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="18">
-        <v>45278</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="19">
-        <v>15000</v>
-      </c>
-      <c r="F8" s="19"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="20">
-        <v>45283</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="21">
-        <v>10000</v>
-      </c>
-      <c r="F9" s="21"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="18">
-        <v>45322</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="19">
-        <v>1500</v>
-      </c>
-      <c r="F10" s="19"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="20">
-        <v>45336</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="E11" s="21">
-        <v>12000</v>
-      </c>
-      <c r="F11" s="21"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="18">
-        <v>45368</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="19">
-        <v>5000</v>
-      </c>
-      <c r="F12" s="19"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="20">
-        <v>45466</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" s="21">
-        <v>10000</v>
-      </c>
-      <c r="F13" s="21"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="18">
-        <v>45647</v>
-      </c>
-      <c r="B14" s="19"/>
-      <c r="C14" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" s="19">
-        <v>10200</v>
-      </c>
-      <c r="F14" s="19"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="20">
-        <v>45647</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="21">
-        <v>10000</v>
-      </c>
-      <c r="F15" s="21"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="18">
-        <v>46123</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="19">
-        <v>80000</v>
-      </c>
-      <c r="F16" s="19"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="20">
-        <v>46202</v>
-      </c>
-      <c r="B17" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="21">
-        <v>160000</v>
-      </c>
-      <c r="F17" s="21"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="15">
-        <v>46221</v>
-      </c>
-      <c r="B18" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="C18" s="24" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="E18" s="24">
-        <v>92500</v>
-      </c>
-      <c r="F18" s="24"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="14">
-        <v>46221</v>
-      </c>
-      <c r="B19" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="C19" s="26" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="E19" s="26">
-        <v>38000</v>
-      </c>
-      <c r="F19" s="26"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="15"/>
-      <c r="B20" s="24"/>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="16"/>
-      <c r="B21" s="27"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="E21" s="26">
-        <f>SUM(E2:E20)</f>
-        <v>579080</v>
-      </c>
-      <c r="F21" s="26">
-        <f>SUM(F2:F20)</f>
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C16">
-      <formula1>Financing</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.140625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="27.28515625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="23.140625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="31.42578125" style="2" customWidth="1"/>
-    <col min="5" max="6" width="19.140625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9.140625" style="2"/>
-    <col min="8" max="8" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="2"/>
+    <col min="1" max="1" width="16.140625" style="22" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" style="22" customWidth="1"/>
+    <col min="3" max="3" width="23.140625" style="22" customWidth="1"/>
+    <col min="4" max="4" width="31.42578125" style="22" customWidth="1"/>
+    <col min="5" max="6" width="19.140625" style="22" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="22"/>
+    <col min="8" max="8" width="14" style="22" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="9" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:8" s="20" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="14" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1586,35 +1487,35 @@
       <c r="A2" s="15">
         <v>45473</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4">
+      <c r="E2" s="16"/>
+      <c r="F2" s="16">
         <v>60000</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="14">
+      <c r="A3" s="17">
         <v>46033</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6">
+      <c r="E3" s="18"/>
+      <c r="F3" s="18">
         <f>60000-14650</f>
         <v>45350</v>
       </c>
@@ -1623,35 +1524,35 @@
       <c r="A4" s="15">
         <v>45853</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4">
+      <c r="E4" s="16"/>
+      <c r="F4" s="16">
         <v>300000</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="14">
+      <c r="A5" s="17">
         <v>45853</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6">
+      <c r="E5" s="18"/>
+      <c r="F5" s="18">
         <v>120000</v>
       </c>
     </row>
@@ -1659,35 +1560,35 @@
       <c r="A6" s="15">
         <v>46066</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4">
+      <c r="E6" s="16"/>
+      <c r="F6" s="16">
         <v>190000</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="14">
+      <c r="A7" s="17">
         <v>46112</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6">
+      <c r="E7" s="18"/>
+      <c r="F7" s="18">
         <v>10000</v>
       </c>
     </row>
@@ -1695,113 +1596,133 @@
       <c r="A8" s="15">
         <v>46157</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4">
+      <c r="E8" s="16"/>
+      <c r="F8" s="16">
         <v>10000</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="14">
+      <c r="A9" s="17">
         <v>46225</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C9" s="6" t="s">
+      <c r="B9" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6">
+      <c r="E9" s="18"/>
+      <c r="F9" s="18">
         <v>14650</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="15"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="A10" s="12">
+        <v>46234</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="21"/>
+      <c r="F10" s="21">
+        <v>14000</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="14"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
+      <c r="A11" s="11">
+        <v>46239</v>
+      </c>
+      <c r="B11" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="23" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="23" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="23"/>
+      <c r="F11" s="23">
+        <v>3000</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="15"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="H12" s="28"/>
+      <c r="A12" s="12"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="H12" s="25"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="14"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
-      <c r="D13" s="6"/>
-      <c r="E13" s="6"/>
-      <c r="F13" s="6"/>
+      <c r="A13" s="11"/>
+      <c r="B13" s="23"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="15"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="14"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
+      <c r="A15" s="11"/>
+      <c r="B15" s="24"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="15"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
+      <c r="A16" s="12"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6">
+      <c r="B17" s="24"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23">
         <f>SUM(E2:E16)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="23">
         <f>SUM(F2:F16)</f>
-        <v>750000</v>
+        <v>767000</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C18:C22 C2:C16">
       <formula1>Investing</formula1>
     </dataValidation>
@@ -1813,20 +1734,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" style="11" customWidth="1"/>
-    <col min="2" max="2" width="33.85546875" style="13" customWidth="1"/>
-    <col min="3" max="3" width="62.5703125" style="11" customWidth="1"/>
-    <col min="4" max="16384" width="9.140625" style="11"/>
+    <col min="1" max="1" width="11.7109375" style="8" customWidth="1"/>
+    <col min="2" max="2" width="33.85546875" style="10" customWidth="1"/>
+    <col min="3" max="3" width="62.5703125" style="8" customWidth="1"/>
+    <col min="4" max="16384" width="9.140625" style="8"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="7" t="s">
         <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -1834,79 +1755,90 @@
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="9" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="9" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C7" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="33" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+    <row r="9" spans="1:3" ht="33" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C9" s="9" t="s">
         <v>18</v>
       </c>
     </row>

--- a/NBFC-MF/FinancingInvesting.xlsx
+++ b/NBFC-MF/FinancingInvesting.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="82">
   <si>
     <t>Date</t>
   </si>
@@ -263,6 +263,15 @@
   </si>
   <si>
     <t>PunfamFoods-5aug-01</t>
+  </si>
+  <si>
+    <t>Bor-Aboong-14aug-01</t>
+  </si>
+  <si>
+    <t>gold mortgage to ibeyaima</t>
+  </si>
+  <si>
+    <t>goldloan-ibeyaima-01</t>
   </si>
 </sst>
 </file>
@@ -1330,48 +1339,58 @@
       <c r="F22" s="16"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A23" s="12">
+      <c r="A23" s="15">
         <v>46234</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D23" s="21" t="s">
+      <c r="D23" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="E23" s="21">
+      <c r="E23" s="16">
         <v>20000</v>
       </c>
-      <c r="F23" s="21"/>
+      <c r="F23" s="16"/>
       <c r="G23" s="25"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A24" s="12">
+      <c r="A24" s="15">
         <v>46234</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D24" s="21" t="s">
+      <c r="D24" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="E24" s="21">
+      <c r="E24" s="16">
         <v>3000</v>
       </c>
-      <c r="F24" s="21"/>
+      <c r="F24" s="16"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="12"/>
-      <c r="B25" s="21"/>
-      <c r="C25" s="21"/>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21"/>
+      <c r="A25" s="12">
+        <v>46248</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="21">
+        <v>10000</v>
+      </c>
       <c r="F25" s="21"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
@@ -1423,7 +1442,7 @@
       </c>
       <c r="E31" s="23">
         <f>SUM(E2:E30)</f>
-        <v>661880</v>
+        <v>671880</v>
       </c>
       <c r="F31" s="23">
         <f>SUM(F2:F22)</f>
@@ -1437,7 +1456,7 @@
       <c r="G33" s="25"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="MJHUm5W/iuw+KYMBQeUmJSJlW+mJz07/RWmQxuj0cM+K7FMztoOwvgHi97SjfCIIRbe7ei/dcr5MUb+C/E0g0w==" saltValue="L2uZANE6DVQeaB2R+ucd8A==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="Rn199iDJz2NV6anJxz+tfCNhRAG9d5R5/yMwX4WIjyuWORXyueeiocaXOLAWbUySGDJVXWW79aYGi87lnxkq5g==" saltValue="o7uUGjYW/WMfLxeD2p5duQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C18">
       <formula1>Financing</formula1>
@@ -1629,48 +1648,58 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="12">
+      <c r="A10" s="15">
         <v>46234</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="E10" s="21"/>
-      <c r="F10" s="21">
+      <c r="E10" s="16"/>
+      <c r="F10" s="16">
         <v>14000</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="11">
+      <c r="A11" s="17">
         <v>46239</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23">
+      <c r="E11" s="18"/>
+      <c r="F11" s="18">
         <v>3000</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="12"/>
-      <c r="B12" s="21"/>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21"/>
+      <c r="A12" s="12">
+        <v>46248</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="21" t="s">
+        <v>80</v>
+      </c>
       <c r="E12" s="21"/>
-      <c r="F12" s="21"/>
+      <c r="F12" s="21">
+        <v>20000</v>
+      </c>
       <c r="H12" s="25"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -1718,10 +1747,11 @@
       </c>
       <c r="F17" s="23">
         <f>SUM(F2:F16)</f>
-        <v>767000</v>
+        <v>787000</v>
       </c>
     </row>
   </sheetData>
+  <sheetProtection algorithmName="SHA-512" hashValue="b/3d101tvhA2RCRRAR261u+uiEZLe+YnaLh87ar96s17DJ2qHpcJ+elIGzPLh41sahi+ZBMXT82P0qMvzk/88w==" saltValue="wP7atpJRqj+fDevF9/C48Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C18:C22 C2:C16">
       <formula1>Investing</formula1>

--- a/NBFC-MF/FinancingInvesting.xlsx
+++ b/NBFC-MF/FinancingInvesting.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Depositors" sheetId="5" r:id="rId1"/>
@@ -13,8 +13,8 @@
     <sheet name="list" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="Financing">list!$B$7:$B$9</definedName>
-    <definedName name="Investing">list!$B$2:$B$6</definedName>
+    <definedName name="Financing">list!$B$8:$B$10</definedName>
+    <definedName name="Investing">list!$B$2:$B$7</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="84">
   <si>
     <t>Date</t>
   </si>
@@ -268,10 +268,16 @@
     <t>Bor-Aboong-14aug-01</t>
   </si>
   <si>
-    <t>gold mortgage to ibeyaima</t>
-  </si>
-  <si>
-    <t>goldloan-ibeyaima-01</t>
+    <t>Recover</t>
+  </si>
+  <si>
+    <t>Loan Recovery</t>
+  </si>
+  <si>
+    <t>Bor-Aboong-24aug-01</t>
+  </si>
+  <si>
+    <t>Bor-Aboong-2aug-01</t>
   </si>
 </sst>
 </file>
@@ -851,56 +857,60 @@
       <c r="E8" s="18"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="18"/>
-      <c r="B9" s="18"/>
+      <c r="A9" s="17">
+        <v>46236</v>
+      </c>
+      <c r="B9" s="18">
+        <v>50000</v>
+      </c>
       <c r="C9" s="18"/>
       <c r="D9" s="18"/>
       <c r="E9" s="18"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="18"/>
+      <c r="A10" s="17"/>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
       <c r="D10" s="18"/>
       <c r="E10" s="18"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="18"/>
+      <c r="A11" s="17"/>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
       <c r="E11" s="18"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="18"/>
+      <c r="A12" s="17"/>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
       <c r="E12" s="18"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="18"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
       <c r="E13" s="18"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="18"/>
+      <c r="A14" s="17"/>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
       <c r="E14" s="18"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="18"/>
+      <c r="A15" s="17"/>
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
       <c r="E15" s="18"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="18"/>
+      <c r="A16" s="17"/>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
@@ -912,7 +922,7 @@
       </c>
       <c r="B17" s="18">
         <f>SUM(B2:B16)</f>
-        <v>131000</v>
+        <v>181000</v>
       </c>
       <c r="C17" s="18">
         <f>SUM(C2:C16)</f>
@@ -928,7 +938,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.140625" style="22" customWidth="1"/>
@@ -936,9 +946,8 @@
     <col min="3" max="3" width="23.140625" style="22" customWidth="1"/>
     <col min="4" max="4" width="31.42578125" style="22" customWidth="1"/>
     <col min="5" max="6" width="19.140625" style="22" customWidth="1"/>
-    <col min="7" max="7" width="14" style="22" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.42578125" style="22" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="22"/>
+    <col min="7" max="7" width="19.42578125" style="22" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" s="20" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1300,7 +1309,6 @@
         <v>92500</v>
       </c>
       <c r="F20" s="16"/>
-      <c r="G20" s="25"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="17">
@@ -1374,47 +1382,79 @@
         <v>3000</v>
       </c>
       <c r="F24" s="16"/>
+      <c r="G24" s="25"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="12">
+      <c r="A25" s="15">
+        <v>46236</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="16">
+        <v>50000</v>
+      </c>
+      <c r="F25" s="16"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="12">
         <v>46248</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B26" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="C26" s="21" t="s">
         <v>13</v>
       </c>
-      <c r="D25" s="21" t="s">
+      <c r="D26" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="21">
+      <c r="E26" s="21">
         <v>10000</v>
       </c>
-      <c r="F25" s="21"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A26" s="12"/>
-      <c r="B26" s="21"/>
-      <c r="C26" s="21"/>
-      <c r="D26" s="21"/>
-      <c r="E26" s="21"/>
       <c r="F26" s="21"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A27" s="12"/>
-      <c r="B27" s="21"/>
-      <c r="C27" s="21"/>
-      <c r="D27" s="21"/>
-      <c r="E27" s="21"/>
+      <c r="A27" s="12">
+        <v>46262</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="21">
+        <v>7000</v>
+      </c>
       <c r="F27" s="21"/>
+      <c r="G27" s="25"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A28" s="12"/>
-      <c r="B28" s="21"/>
-      <c r="C28" s="21"/>
-      <c r="D28" s="21"/>
-      <c r="E28" s="21"/>
+      <c r="A28" s="12">
+        <v>46262</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" s="21">
+        <v>4230</v>
+      </c>
       <c r="F28" s="21"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
@@ -1434,29 +1474,30 @@
       <c r="F30" s="21"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A31" s="13"/>
-      <c r="B31" s="24"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="13" t="s">
+      <c r="A31" s="12"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" s="13"/>
+      <c r="B32" s="24"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="E31" s="23">
-        <f>SUM(E2:E30)</f>
-        <v>671880</v>
-      </c>
-      <c r="F31" s="23">
+      <c r="E32" s="23">
+        <f>SUM(E2:E31)</f>
+        <v>733110</v>
+      </c>
+      <c r="F32" s="23">
         <f>SUM(F2:F22)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G32" s="25"/>
-    </row>
-    <row r="33" spans="7:7" x14ac:dyDescent="0.3">
-      <c r="G33" s="25"/>
-    </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Rn199iDJz2NV6anJxz+tfCNhRAG9d5R5/yMwX4WIjyuWORXyueeiocaXOLAWbUySGDJVXWW79aYGi87lnxkq5g==" saltValue="o7uUGjYW/WMfLxeD2p5duQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C18">
       <formula1>Financing</formula1>
@@ -1519,6 +1560,7 @@
       <c r="F2" s="16">
         <v>60000</v>
       </c>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="17">
@@ -1538,6 +1580,7 @@
         <f>60000-14650</f>
         <v>45350</v>
       </c>
+      <c r="H3" s="21"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="15">
@@ -1556,6 +1599,7 @@
       <c r="F4" s="16">
         <v>300000</v>
       </c>
+      <c r="H4" s="23"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="17">
@@ -1679,27 +1723,17 @@
         <v>72</v>
       </c>
       <c r="E11" s="18"/>
-      <c r="F11" s="18">
+      <c r="F11" s="23">
         <v>3000</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="12">
-        <v>46248</v>
-      </c>
-      <c r="B12" s="21" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>80</v>
-      </c>
+      <c r="A12" s="12"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
       <c r="E12" s="21"/>
-      <c r="F12" s="21">
-        <v>20000</v>
-      </c>
+      <c r="F12" s="21"/>
       <c r="H12" s="25"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
@@ -1747,11 +1781,10 @@
       </c>
       <c r="F17" s="23">
         <f>SUM(F2:F16)</f>
-        <v>787000</v>
+        <v>767000</v>
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="b/3d101tvhA2RCRRAR261u+uiEZLe+YnaLh87ar96s17DJ2qHpcJ+elIGzPLh41sahi+ZBMXT82P0qMvzk/88w==" saltValue="wP7atpJRqj+fDevF9/C48Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C18:C22 C2:C16">
       <formula1>Investing</formula1>
@@ -1764,7 +1797,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.7109375" style="8" customWidth="1"/>
@@ -1807,14 +1840,14 @@
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>9</v>
+      <c r="B4" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -1822,53 +1855,64 @@
         <v>7</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C6" s="9" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C7" s="6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C8" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B9" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C9" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="33" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+    <row r="10" spans="1:3" ht="33" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C10" s="9" t="s">
         <v>18</v>
       </c>
     </row>
